--- a/artfynd/A 60565-2022 artfynd.xlsx
+++ b/artfynd/A 60565-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60565-2022 artfynd.xlsx
+++ b/artfynd/A 60565-2022 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105993798</v>
+        <v>105992140</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87, Jmt</t>
+          <t>Söder om Moarsved vid väg 87 , Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494202.1162221654</v>
+        <v>494050</v>
       </c>
       <c r="R2" t="n">
-        <v>7008495.360092859</v>
+        <v>7008498</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,24 +746,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Garnlav på en gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Enstaka bålar av garnlav på en gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Flerskiktad och luckig olikåldrig grandominerad skog med inslag av tall och björk på frisk-fuktig mark. Måttlig förekomst av död ved.</t>
+          <t>Äldre flerskiktad och luckig olikåldrig grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark. Här finns bitvis gott om klenvuxna granar. Måttlig förekomst av död ved. Spår av hackspett förekommer.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -801,6 +786,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En äldre gran.</t>
+        </is>
+      </c>
       <c r="AM2" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -808,7 +798,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # En äldre gran.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -826,19 +816,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105992140</v>
+        <v>105993798</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -865,14 +850,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87 , Jmt</t>
+          <t>Söder om Moarsved vid väg 87, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494050.3107072924</v>
+        <v>494202</v>
       </c>
       <c r="R3" t="n">
-        <v>7008498.34349319</v>
+        <v>7008495</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -902,24 +887,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på en gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Garnlav på en gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,7 +914,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig olikåldrig grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark. Här finns bitvis gott om klenvuxna granar. Måttlig förekomst av död ved. Spår av hackspett förekommer.</t>
+          <t>Flerskiktad och luckig olikåldrig grandominerad skog med inslag av tall och björk på frisk-fuktig mark. Måttlig förekomst av död ved.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -952,11 +927,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>En äldre gran.</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -964,7 +934,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # En äldre gran.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -982,69 +952,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105995866</v>
+        <v>105995751</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87, Bringåsen, Kyrkås, Jmt</t>
+          <t>Söder om Moarsved vid väg 87, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494209.3541963492</v>
+        <v>494202</v>
       </c>
       <c r="R4" t="n">
-        <v>7008500.310303948</v>
+        <v>7008513</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1071,24 +1023,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Observation av lätet från två talltitor. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1097,6 +1039,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1108,6 +1051,26 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Flerskiktad och luckig olikåldrig grandominerad skog med inslag av tall och björk på frisk-fuktig mark. Måttlig förekomst av död ved.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1125,19 +1088,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105999064</v>
+        <v>105997290</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1168,10 +1126,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494474.5271319833</v>
+        <v>494525</v>
       </c>
       <c r="R5" t="n">
-        <v>7008474.578277845</v>
+        <v>7008479</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1201,24 +1159,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Garnlav på en gammal gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1253,7 +1201,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En gammal gran.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1263,7 +1211,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies # En gammal gran.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1281,19 +1229,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105995751</v>
+        <v>105998960</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1324,10 +1267,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494202.148634611</v>
+        <v>494483</v>
       </c>
       <c r="R6" t="n">
-        <v>7008513.40800454</v>
+        <v>7008489</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1357,24 +1300,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1394,7 +1327,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Flerskiktad och luckig olikåldrig grandominerad skog med inslag av tall och björk på frisk-fuktig mark. Måttlig förekomst av död ved.</t>
+          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på fuktig och frisk-fuktig mark. Måttlig förekomst av död ved.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1432,61 +1365,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105997494</v>
+        <v>105999064</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87 , Jmt</t>
+          <t>Söder om Moarsved vid väg 87, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494482.2234932908</v>
+        <v>494474</v>
       </c>
       <c r="R7" t="n">
-        <v>7008483.589166974</v>
+        <v>7008474</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1513,24 +1436,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Revlummer i äldre granskog. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1551,6 +1464,31 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Måttlig förekomst av död ved.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1568,19 +1506,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105997290</v>
+        <v>105999145</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1611,10 +1544,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494525.5911953039</v>
+        <v>494438</v>
       </c>
       <c r="R8" t="n">
-        <v>7008479.454516516</v>
+        <v>7008459</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1644,24 +1577,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Garnlav på en gammal gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1696,7 +1619,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>En gammal gran.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1706,7 +1629,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # En gammal gran.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1724,19 +1647,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105998960</v>
+        <v>105999176</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1759,21 +1677,25 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87, Jmt</t>
+          <t>Söder om Moarsved vid väg 87, Bringåsen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494483.1356119447</v>
+        <v>494414</v>
       </c>
       <c r="R9" t="n">
-        <v>7008488.550826261</v>
+        <v>7008461</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1800,24 +1722,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Långväxt garnlav på flera granar. Vissa bålar är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1837,7 +1749,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på fuktig och frisk-fuktig mark. Måttlig förekomst av död ved.</t>
+          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Måttlig förekomst av död ved.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1850,6 +1762,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM9" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -1857,7 +1774,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1875,19 +1792,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105999176</v>
+        <v>105999220</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1910,25 +1822,21 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87, Bringåsen, Kyrkås, Jmt</t>
+          <t>Söder om Moarsved vid väg 87, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494413.5072449186</v>
+        <v>494404</v>
       </c>
       <c r="R10" t="n">
-        <v>7008460.695959454</v>
+        <v>7008477</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1955,24 +1863,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Vissa bålar är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Måttlig påväxt av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2005,11 +1903,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM10" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2017,7 +1910,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2035,19 +1928,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105999145</v>
+        <v>105999222</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2074,14 +1962,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87, Jmt</t>
+          <t>Söder om Moarsved vid väg 87 , Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494437.9032917137</v>
+        <v>494446</v>
       </c>
       <c r="R11" t="n">
-        <v>7008459.300220608</v>
+        <v>7008438</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2111,24 +1999,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2148,7 +2026,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Måttlig förekomst av död ved.</t>
+          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på fuktig och frisk-fuktig mark. Måttlig förekomst av död ved.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2161,11 +2039,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM11" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2173,7 +2046,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2194,16 +2067,11 @@
         <v>105999250</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2234,10 +2102,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494486.1966181844</v>
+        <v>494486</v>
       </c>
       <c r="R12" t="n">
-        <v>7008428.986477648</v>
+        <v>7008429</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2267,19 +2135,9 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-01-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2342,69 +2200,55 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105999153</v>
+        <v>105999303</v>
       </c>
       <c r="B13" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87, Bringåsen, Kyrkås, Jmt</t>
+          <t>Söder om Moarsved vid väg 87, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494413.5072449186</v>
+        <v>494511</v>
       </c>
       <c r="R13" t="n">
-        <v>7008460.695959454</v>
+        <v>7008451</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2431,24 +2275,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st. talltitor i äldre granskog. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Långväxt garnlav på gran. Vissa bålar är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2457,6 +2291,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2467,7 +2302,27 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Måttlig förekomst av död ved.</t>
+          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på fuktig och frisk-fuktig mark. Måttlig förekomst av död ved.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2485,15 +2340,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105999222</v>
+        <v>105992530</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2501,40 +2351,53 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87 , Jmt</t>
+          <t>Söder om Moarsved vid väg 87 , Bringåsen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494445.9996056877</v>
+        <v>494042</v>
       </c>
       <c r="R14" t="n">
-        <v>7008438.079558863</v>
+        <v>7008507</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2561,24 +2424,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Synobservation av två talltitor. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2587,7 +2440,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2598,27 +2450,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på fuktig och frisk-fuktig mark. Måttlig förekomst av död ved.</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Äldre flerskiktad och luckig olikåldrig grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark. Här finns bitvis gott om klenvuxna granar. Måttlig förekomst av död ved. Spår av hackspett förekommer.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2636,15 +2468,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105999303</v>
+        <v>105995866</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2652,44 +2479,53 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87, Jmt</t>
+          <t>Söder om Moarsved vid väg 87, Bringåsen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494510.6328289391</v>
+        <v>494209</v>
       </c>
       <c r="R15" t="n">
-        <v>7008451.054030739</v>
+        <v>7008500</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2716,24 +2552,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Vissa bålar är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Observation av lätet från två talltitor. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2742,7 +2568,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2753,27 +2578,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på fuktig och frisk-fuktig mark. Måttlig förekomst av död ved.</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Flerskiktad och luckig olikåldrig grandominerad skog med inslag av tall och björk på frisk-fuktig mark. Måttlig förekomst av död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2791,15 +2596,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105999220</v>
+        <v>105999153</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2807,40 +2607,53 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87, Jmt</t>
+          <t>Söder om Moarsved vid väg 87, Bringåsen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494404.4989613732</v>
+        <v>494414</v>
       </c>
       <c r="R16" t="n">
-        <v>7008476.954907262</v>
+        <v>7008461</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2867,24 +2680,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Måttlig påväxt av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Synobservation av 2 st. talltitor i äldre granskog. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2893,7 +2696,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2905,26 +2707,6 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Måttlig förekomst av död ved.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2942,51 +2724,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105992530</v>
+        <v>105997494</v>
       </c>
       <c r="B17" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2994,14 +2763,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söder om Moarsved vid väg 87 , Bringåsen, Kyrkås, Jmt</t>
+          <t>Söder om Moarsved vid väg 87 , Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494042.194662115</v>
+        <v>494482</v>
       </c>
       <c r="R17" t="n">
-        <v>7008507.382451728</v>
+        <v>7008484</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3031,24 +2800,14 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Synobservation av två talltitor. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
+          <t>Revlummer i äldre granskog. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 60565-2022.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3057,6 +2816,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3067,7 +2827,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig olikåldrig grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark. Här finns bitvis gott om klenvuxna granar. Måttlig förekomst av död ved. Spår av hackspett förekommer.</t>
+          <t>Flerskiktad och luckig grandominerad äldre skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Måttlig förekomst av död ved.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 60565-2022 artfynd.xlsx
+++ b/artfynd/A 60565-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -813,6 +818,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105992140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -949,6 +959,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105993798</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1085,6 +1100,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105995751</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1226,6 +1246,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105997290</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1362,6 +1387,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105998960</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1503,6 +1533,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105999064</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1644,6 +1679,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105999145</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1789,6 +1829,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105999176</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1925,6 +1970,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105999220</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2061,6 +2111,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105999222</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2197,6 +2252,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105999250</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2337,6 +2397,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105999303</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2465,6 +2530,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105992530</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2593,6 +2663,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105995866</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2721,6 +2796,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105999153</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2842,8 +2922,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105997494</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>